--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20232.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -73,19 +73,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CHONKOA</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
     <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
@@ -580,16 +571,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="H2">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -603,16 +597,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>92.31</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -668,13 +665,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H2">
         <v>8.800000000000001</v>
@@ -694,16 +691,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>96.15000000000001</v>
+        <v>92.31</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -713,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -745,47 +742,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920393</v>
+        <v>20330051920132</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920132</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20232.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -76,10 +76,28 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
     <t>NOYOLA</t>
   </si>
   <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
   </si>
 </sst>
 </file>
@@ -674,7 +692,7 @@
         <v>96</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,16 +709,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>92.31</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -710,7 +728,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -748,10 +766,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -761,6 +779,52 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920390</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920067</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
